--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-member.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-member.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-member.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-member.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FR Core Organization Extension - Membre d'organisation</t>
+    <t>FR Core Organization Extension - quelles sont les entités qui font partie de l'organisation</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension permettant de définir des membres d'une organisation.</t>
+    <t>Extension permettant de définir des membres d'une organisation. Les membres sont des organisations filles de la ressources. C'est la relation inverse de partOf.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization#Organization</t>
+    <t>element:Organization</t>
   </si>
   <si>
     <t>ID</t>
@@ -358,7 +358,7 @@
     <t>valueReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
 </sst>
